--- a/1_PREPARE_TRAIN_UNET_DATA/TriuksmaiAnotacijosDuomenyse2023/05_Anotavimo_logas.xlsx
+++ b/1_PREPARE_TRAIN_UNET_DATA/TriuksmaiAnotacijosDuomenyse2023/05_Anotavimo_logas.xlsx
@@ -8,24 +8,117 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kesju\DI\2025_ZIVEO\PROJECT_TRAIN_UNET\1_PREPARE_TRAIN_UNET_DATA\TriuksmaiAnotacijosDuomenyse2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4D8AFA7-3C95-449A-975F-7A7F4002AA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF5D815-098E-42FD-B012-9274C4AB3472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="sarasas" sheetId="1" r:id="rId1"/>
+    <sheet name="logas" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">logas!$A$1:$M$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sarasas!$A$1:$Z$1</definedName>
+  </definedNames>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
+  <si>
+    <t>filename</t>
+  </si>
+  <si>
+    <t>samples</t>
+  </si>
+  <si>
+    <t>basename</t>
+  </si>
+  <si>
+    <t>quality</t>
+  </si>
+  <si>
+    <t>noni</t>
+  </si>
+  <si>
+    <t>tag</t>
+  </si>
+  <si>
+    <t>N,J,Ž</t>
+  </si>
+  <si>
+    <t>mark</t>
+  </si>
+  <si>
+    <t>rpk_cnt</t>
+  </si>
+  <si>
+    <t>hN</t>
+  </si>
+  <si>
+    <t>hS</t>
+  </si>
+  <si>
+    <t>hV</t>
+  </si>
+  <si>
+    <t>hU</t>
+  </si>
+  <si>
+    <t>mlS</t>
+  </si>
+  <si>
+    <t>mlV</t>
+  </si>
+  <si>
+    <t>mlU</t>
+  </si>
+  <si>
+    <t>h_nz_cnt</t>
+  </si>
+  <si>
+    <t>h_nz_len</t>
+  </si>
+  <si>
+    <t>h_nz_frac</t>
+  </si>
+  <si>
+    <t>ml_nz_cnt</t>
+  </si>
+  <si>
+    <t>ml_nz_len</t>
+  </si>
+  <si>
+    <t>ml_nz_frac</t>
+  </si>
+  <si>
+    <t>flags</t>
+  </si>
+  <si>
+    <t>recordingId</t>
+  </si>
+  <si>
+    <t>userId</t>
+  </si>
+  <si>
+    <t>comment</t>
+  </si>
+  <si>
+    <t>1103_0</t>
+  </si>
+  <si>
+    <t>1742295.469</t>
+  </si>
+  <si>
+    <t>EXTERNALLY_ANNOTATED,FOR_EXTERNAL_ANNOTATING</t>
+  </si>
+  <si>
+    <t>67d9543186cf219834695639</t>
+  </si>
+  <si>
+    <t>607efbd094e6ea3b5a1ab959</t>
+  </si>
   <si>
     <t>nr</t>
   </si>
@@ -45,43 +138,13 @@
     <t>AI_DATASET</t>
   </si>
   <si>
-    <t>basename</t>
-  </si>
-  <si>
     <t>Comments</t>
   </si>
   <si>
-    <t>file_name</t>
-  </si>
-  <si>
     <t>rec_id</t>
   </si>
   <si>
     <t>uid</t>
-  </si>
-  <si>
-    <t>Žygimantas</t>
-  </si>
-  <si>
-    <t>Nika</t>
-  </si>
-  <si>
-    <t>1740295.071</t>
-  </si>
-  <si>
-    <t>Igno Griskeviciaus su nepagautomis V</t>
-  </si>
-  <si>
-    <t>1742295.469</t>
-  </si>
-  <si>
-    <t>1103_0</t>
-  </si>
-  <si>
-    <t>1742319.328</t>
-  </si>
-  <si>
-    <t>1742362.474</t>
   </si>
 </sst>
 </file>
@@ -89,8 +152,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="0.0&quot;%&quot;"/>
+    <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -159,14 +222,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -182,6 +243,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -462,239 +524,290 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X5"/>
+  <dimension ref="A1:Z2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.36328125" customWidth="1"/>
-    <col min="6" max="6" width="32.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="40.7265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="7" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.6328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="48.90625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="24.6328125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="25.1796875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2">
+        <v>128000</v>
+      </c>
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>9</v>
+      </c>
+      <c r="I2">
+        <v>665</v>
+      </c>
+      <c r="J2">
+        <v>661</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>4</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>9</v>
+      </c>
+      <c r="R2">
+        <v>6747</v>
+      </c>
+      <c r="S2" s="2">
+        <v>5.2710937500000004</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2" s="8">
+        <v>0</v>
+      </c>
+      <c r="W2" t="s">
+        <v>28</v>
+      </c>
+      <c r="X2" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Z1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.6328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="25.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="9" t="s">
+      <c r="A1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
-      <c r="W1" s="5"/>
-      <c r="X1" s="5"/>
+      <c r="D1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A2" s="6">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1"/>
-      <c r="X2" s="4"/>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A3" s="6">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="1"/>
-      <c r="S3" s="1"/>
-      <c r="T3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="1"/>
-      <c r="W3" s="1"/>
-      <c r="X3" s="4"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A4" s="6">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="1"/>
-      <c r="W4" s="1"/>
-      <c r="X4" s="4"/>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A5" s="6">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
-      <c r="T5" s="1"/>
-      <c r="U5" s="1"/>
-      <c r="V5" s="1"/>
-      <c r="W5" s="1"/>
-      <c r="X5" s="4"/>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="4"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="6"/>
+      <c r="L2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" t="s">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M1" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>